--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
@@ -352,49 +352,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost_per_year</t>
+          <t>mean_visits_cost</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_cost_per_year</t>
+          <t>min_visits_cost</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_cost_per_year</t>
+          <t>max_visits_cost</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_cost_per_year</t>
+          <t>sd_visits_cost</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_cost_per_year</t>
+          <t>median_visits_cost</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_cost_per_year</t>
+          <t>q1_visits_cost</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_cost_per_year</t>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1072.13</v>
+        <v>894.16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -403,16 +423,28 @@
         <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>936.34</v>
+        <v>893.83</v>
       </c>
       <c r="E2">
-        <v>840</v>
+        <v>656.75</v>
       </c>
       <c r="F2">
-        <v>443.96</v>
+        <v>252</v>
       </c>
       <c r="G2">
-        <v>1428</v>
+        <v>1241.96</v>
+      </c>
+      <c r="H2">
+        <v>18133</v>
+      </c>
+      <c r="I2">
+        <v>6.637737846441591</v>
+      </c>
+      <c r="J2">
+        <v>881.1494043873493</v>
+      </c>
+      <c r="K2">
+        <v>907.1705956126507</v>
       </c>
     </row>
   </sheetData>
@@ -422,49 +454,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost_per_year</t>
+          <t>mean_visits_cost</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_cost_per_year</t>
+          <t>min_visits_cost</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_cost_per_year</t>
+          <t>max_visits_cost</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_cost_per_year</t>
+          <t>sd_visits_cost</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_cost_per_year</t>
+          <t>median_visits_cost</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_cost_per_year</t>
+          <t>q1_visits_cost</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_cost_per_year</t>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1089.03</v>
+        <v>919.2</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -473,16 +525,28 @@
         <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>933.88</v>
+        <v>893.47</v>
       </c>
       <c r="E2">
-        <v>851.98</v>
+        <v>672</v>
       </c>
       <c r="F2">
-        <v>462</v>
+        <v>294</v>
       </c>
       <c r="G2">
-        <v>1436.37</v>
+        <v>1260</v>
+      </c>
+      <c r="H2">
+        <v>17639</v>
+      </c>
+      <c r="I2">
+        <v>6.72733407018109</v>
+      </c>
+      <c r="J2">
+        <v>906.0137626381741</v>
+      </c>
+      <c r="K2">
+        <v>932.386237361826</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>894.16</v>
+        <v>761.71</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>893.83</v>
+        <v>850.51</v>
       </c>
       <c r="E2">
-        <v>656.75</v>
+        <v>504</v>
       </c>
       <c r="F2">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="G2">
-        <v>1241.96</v>
+        <v>1050</v>
       </c>
       <c r="H2">
         <v>18133</v>
       </c>
       <c r="I2">
-        <v>6.637737846441591</v>
+        <v>6.316035952896007</v>
       </c>
       <c r="J2">
-        <v>881.1494043873493</v>
+        <v>749.3299706045719</v>
       </c>
       <c r="K2">
-        <v>907.1705956126507</v>
+        <v>774.0900293954281</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>919.2</v>
+        <v>797.87</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>893.47</v>
+        <v>853.73</v>
       </c>
       <c r="E2">
-        <v>672</v>
+        <v>542.4400000000001</v>
       </c>
       <c r="F2">
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="G2">
-        <v>1260</v>
+        <v>1092</v>
       </c>
       <c r="H2">
-        <v>17639</v>
+        <v>17311</v>
       </c>
       <c r="I2">
-        <v>6.72733407018109</v>
+        <v>6.48872643356105</v>
       </c>
       <c r="J2">
-        <v>906.0137626381741</v>
+        <v>785.151440567696</v>
       </c>
       <c r="K2">
-        <v>932.386237361826</v>
+        <v>810.588559432304</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>761.71</v>
+        <v>832.9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>850.51</v>
+        <v>856.4</v>
       </c>
       <c r="E2">
-        <v>504</v>
+        <v>588</v>
       </c>
       <c r="F2">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="G2">
-        <v>1050</v>
+        <v>1134</v>
       </c>
       <c r="H2">
-        <v>18133</v>
+        <v>23106</v>
       </c>
       <c r="I2">
-        <v>6.316035952896007</v>
+        <v>5.633966679156932</v>
       </c>
       <c r="J2">
-        <v>749.3299706045719</v>
+        <v>821.8570497298839</v>
       </c>
       <c r="K2">
-        <v>774.0900293954281</v>
+        <v>843.9429502701161</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>797.87</v>
+        <v>858.88</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -525,28 +525,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>853.73</v>
+        <v>856.73</v>
       </c>
       <c r="E2">
-        <v>542.4400000000001</v>
+        <v>610.14</v>
       </c>
       <c r="F2">
-        <v>210</v>
+        <v>278.75</v>
       </c>
       <c r="G2">
-        <v>1092</v>
+        <v>1149.59</v>
       </c>
       <c r="H2">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="I2">
-        <v>6.48872643356105</v>
+        <v>5.723373887275386</v>
       </c>
       <c r="J2">
-        <v>785.151440567696</v>
+        <v>847.6617873073029</v>
       </c>
       <c r="K2">
-        <v>810.588559432304</v>
+        <v>870.0982126926971</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>832.9</v>
+        <v>1105.73</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>21268.51</v>
       </c>
       <c r="D2">
-        <v>856.4</v>
+        <v>1189.91</v>
       </c>
       <c r="E2">
-        <v>588</v>
+        <v>764.02</v>
       </c>
       <c r="F2">
-        <v>252</v>
+        <v>318.73</v>
       </c>
       <c r="G2">
-        <v>1134</v>
+        <v>1486.39</v>
       </c>
       <c r="H2">
-        <v>23106</v>
+        <v>23007</v>
       </c>
       <c r="I2">
-        <v>5.633966679156932</v>
+        <v>7.844840501724733</v>
       </c>
       <c r="J2">
-        <v>821.8570497298839</v>
+        <v>1090.353586187023</v>
       </c>
       <c r="K2">
-        <v>843.9429502701161</v>
+        <v>1121.106413812977</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>858.88</v>
+        <v>1101.27</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>0.95</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>19934</v>
       </c>
       <c r="D2">
-        <v>856.73</v>
+        <v>1170.37</v>
       </c>
       <c r="E2">
-        <v>610.14</v>
+        <v>760.9400000000001</v>
       </c>
       <c r="F2">
-        <v>278.75</v>
+        <v>336</v>
       </c>
       <c r="G2">
-        <v>1149.59</v>
+        <v>1471.9</v>
       </c>
       <c r="H2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="I2">
-        <v>5.723373887275386</v>
+        <v>7.80906377380908</v>
       </c>
       <c r="J2">
-        <v>847.6617873073029</v>
+        <v>1085.963691434069</v>
       </c>
       <c r="K2">
-        <v>870.0982126926971</v>
+        <v>1116.576308565931</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1105.73</v>
+        <v>832.9</v>
       </c>
       <c r="B2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>21268.51</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1189.91</v>
+        <v>856.4</v>
       </c>
       <c r="E2">
-        <v>764.02</v>
+        <v>588</v>
       </c>
       <c r="F2">
-        <v>318.73</v>
+        <v>252</v>
       </c>
       <c r="G2">
-        <v>1486.39</v>
+        <v>1134</v>
       </c>
       <c r="H2">
-        <v>23007</v>
+        <v>23106</v>
       </c>
       <c r="I2">
-        <v>7.844840501724733</v>
+        <v>5.633966679156932</v>
       </c>
       <c r="J2">
-        <v>1090.353586187023</v>
+        <v>821.8570497298839</v>
       </c>
       <c r="K2">
-        <v>1121.106413812977</v>
+        <v>843.9429502701161</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1101.27</v>
+        <v>858.88</v>
       </c>
       <c r="B2">
-        <v>0.95</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>19934</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1170.37</v>
+        <v>856.73</v>
       </c>
       <c r="E2">
-        <v>760.9400000000001</v>
+        <v>610.14</v>
       </c>
       <c r="F2">
-        <v>336</v>
+        <v>278.75</v>
       </c>
       <c r="G2">
-        <v>1471.9</v>
+        <v>1149.59</v>
       </c>
       <c r="H2">
-        <v>22462</v>
+        <v>22407</v>
       </c>
       <c r="I2">
-        <v>7.80906377380908</v>
+        <v>5.723373887275386</v>
       </c>
       <c r="J2">
-        <v>1085.963691434069</v>
+        <v>847.6617873073029</v>
       </c>
       <c r="K2">
-        <v>1116.576308565931</v>
+        <v>870.0982126926971</v>
       </c>
     </row>
   </sheetData>
